--- a/etl/working/II 2026-06-01.xlsx
+++ b/etl/working/II 2026-06-01.xlsx
@@ -16,11 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,31 +27,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF99"/>
-        <bgColor rgb="00FFFF99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -60,24 +44,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,242 +420,242 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t xml:space="preserve"> Outlook</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t xml:space="preserve"> Ticker</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="A2" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>SWBI</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="A3" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>ULS</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="A4" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="A5" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>ROKU</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="A6" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>SXT</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="A7" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>SITM</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="A8" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>UNH</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="A9" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>SBUX</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="A10" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>ROP</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="A11" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>RBLX</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="A12" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>OLLI</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="A13" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>HCA</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>WING</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>DPZ</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="A16" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>NCLH</t>
         </is>
